--- a/tests/workbooktests/workbooks/test_date.xlsx
+++ b/tests/workbooktests/workbooks/test_date.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFEF087-6DAE-4D61-988B-982D70611DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F935F4B1-8483-4C42-BCBF-7AF6C16EC6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10425" yWindow="-19335" windowWidth="23040" windowHeight="16005" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="qlPeriod" sheetId="1" r:id="rId1"/>
@@ -509,45 +509,45 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" cm="1">
-        <f t="array" ref="A3">_xll.qlPeriodLength(A1)</f>
-        <v>12</v>
+      <c r="A3" t="e" cm="1">
+        <f t="array" aca="1" ref="A3" ca="1">_xll.qlPeriodLength(A1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="str" cm="1">
-        <f t="array" ref="A4">_xll.qlPeriodFrequency(A1)</f>
-        <v>ANNUAL</v>
+      <c r="A4" t="e" cm="1">
+        <f t="array" aca="1" ref="A4" ca="1">_xll.qlPeriodFrequency(A1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5">_xll.qlPeriodFrequency(A2)</f>
-        <v>OTHERFREQUENCY</v>
+      <c r="A5" t="e" cm="1">
+        <f t="array" aca="1" ref="A5" ca="1">_xll.qlPeriodFrequency(A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="str" cm="1">
-        <f t="array" ref="A6">_xll.qlPeriodNormalized(A1)</f>
-        <v>1Y</v>
+      <c r="A6" t="e" cm="1">
+        <f t="array" aca="1" ref="A6" ca="1">_xll.qlPeriodNormalized(A1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="str" cm="1">
-        <f t="array" ref="A7">_xll.qlPeriodNormalized(A2)</f>
-        <v>37D</v>
+      <c r="A7" t="e" cm="1">
+        <f t="array" aca="1" ref="A7" ca="1">_xll.qlPeriodNormalized(A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="str" cm="1">
-        <f t="array" ref="A8">_xll.qlPeriodUnits(A1)</f>
-        <v>MONTHS</v>
+      <c r="A8" t="e" cm="1">
+        <f t="array" aca="1" ref="A8" ca="1">_xll.qlPeriodUnits(A1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="str" cm="1">
-        <f t="array" ref="A9">_xll.qlPeriodUnits(A2)</f>
-        <v>DAYS</v>
+      <c r="A9" t="e" cm="1">
+        <f t="array" aca="1" ref="A9" ca="1">_xll.qlPeriodUnits(A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -592,63 +592,63 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" cm="1">
-        <f t="array" ref="B4">_xll.qlDate(B1,B2,B3)</f>
-        <v>46159</v>
+      <c r="B4" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlDate(B1,B2,B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlDateWeekday(B4)</f>
-        <v>SUNDAY</v>
+      <c r="B5" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlDateWeekday(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" cm="1">
-        <f t="array" ref="B6">_xll.qlDateDayOfMonth(B4)</f>
-        <v>17</v>
+      <c r="B6" t="e" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">_xll.qlDateDayOfMonth(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" cm="1">
-        <f t="array" ref="B7">_xll.qlDateDayOfYear(B4)</f>
-        <v>137</v>
+      <c r="B7" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlDateDayOfYear(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" cm="1">
-        <f t="array" ref="B8">_xll.qlDateMonth(B4)</f>
-        <v>5</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlDateMonth(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" cm="1">
-        <f t="array" ref="B9">_xll.qlDateYear(B4)</f>
-        <v>2026</v>
+      <c r="B9" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlDateYear(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="b" cm="1">
-        <f t="array" ref="B10">_xll.qlDateIsLeap(B9-2)</f>
-        <v>1</v>
+      <c r="B10" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlDateIsLeap(B9-2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -679,36 +679,36 @@
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1" cm="1">
-        <f t="array" ref="B14">_xll.qlDateStartOfMonth(B4)</f>
-        <v>46143</v>
+      <c r="B14" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlDateStartOfMonth(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="1" cm="1">
-        <f t="array" ref="B15">_xll.qlDateEndOfMonth(B4)</f>
-        <v>46173</v>
+      <c r="B15" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlDateEndOfMonth(B4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="b" cm="1">
-        <f t="array" ref="B16">_xll.qlDateIsStartOfMonth(B14)</f>
-        <v>1</v>
+      <c r="B16" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlDateIsStartOfMonth(B14)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="b" cm="1">
-        <f t="array" ref="B17">_xll.qlDateIsEndOfMonth(B15)</f>
-        <v>1</v>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlDateIsEndOfMonth(B15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -723,9 +723,9 @@
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1" cm="1">
-        <f t="array" ref="B19">_xll.qlDateNextWeekday(B4,B18)</f>
-        <v>46161</v>
+      <c r="B19" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">_xll.qlDateNextWeekday(B4,B18)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -740,9 +740,9 @@
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="1" cm="1">
-        <f t="array" ref="B21">_xll.qlDateNthWeekday(B20,B18,B8,B9)</f>
-        <v>46161</v>
+      <c r="B21" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlDateNthWeekday(B20,B18,B8,B9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -787,18 +787,18 @@
       <c r="A4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" cm="1">
-        <f t="array" ref="B4">_xll.qlDateParserParseFormatted(B1,B2)</f>
-        <v>45394</v>
+      <c r="B4" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlDateParserParseFormatted(B1,B2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="3" cm="1">
-        <f t="array" ref="B5">_xll.qlDateParserParseISO(B3)</f>
-        <v>45394</v>
+      <c r="B5" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B5" ca="1">_xll.qlDateParserParseISO(B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -826,9 +826,9 @@
       <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2">_xll.qlPeriodParserParse(B1)</f>
-        <v>15M</v>
+      <c r="B2" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlPeriodParserParse(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
